--- a/employment/04_construction_analysis.xlsx
+++ b/employment/04_construction_analysis.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -791,1330 +791,1330 @@
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>KS</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Hawaii</t>
+          <t>Kansas</t>
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>693984.3749999997</v>
+        <v>579086.8329428637</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>254354.5750042915</v>
+        <v>160194.1532439261</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>195449.4079915882</v>
+        <v>265106.2925847685</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>1192519.342008411</v>
+        <v>893067.3733009589</v>
       </c>
       <c r="G8" s="6" t="n">
-        <v>0.5153777052635589</v>
+        <v>0.6511780870106511</v>
       </c>
       <c r="H8" s="7" t="n">
-        <v>0.02940600100836302</v>
+        <v>0.008568052202735836</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>0.016–0.017</t>
+          <t>0.058–0.069</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>KS</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>579086.8329428637</v>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>160194.1532439261</v>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>428526.4547484969</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>310063.584557146</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>265106.2925847685</v>
+        <v>-179198.1709835092</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>893067.3733009589</v>
+        <v>1036251.080480503</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>0.6511780870106511</v>
-      </c>
-      <c r="H9" s="7" t="n">
-        <v>0.008568052202735836</v>
+        <v>0.2143737848409374</v>
+      </c>
+      <c r="H9" s="8" t="n">
+        <v>0.2094449735891394</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>0.058–0.069</t>
+          <t>0.043–0.049</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>CO</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Connecticut</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>428526.4547484969</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>310063.584557146</v>
+          <t>Colorado</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="n">
+        <v>365281.0386439174</v>
+      </c>
+      <c r="D10" s="4" t="n">
+        <v>56693.05835035787</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>-179198.1709835092</v>
+        <v>254162.644277216</v>
       </c>
       <c r="F10" s="5" t="n">
-        <v>1036251.080480503</v>
+        <v>476399.4330106188</v>
       </c>
       <c r="G10" s="6" t="n">
-        <v>0.2143737848409374</v>
-      </c>
-      <c r="H10" s="8" t="n">
-        <v>0.2094449735891394</v>
+        <v>0.8557117263347711</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>0.0003525505122485738</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>0.043–0.049</t>
+          <t>0.455–0.524</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>CO</t>
+          <t>MI</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Colorado</t>
+          <t>Michigan</t>
         </is>
       </c>
       <c r="C11" s="4" t="n">
-        <v>365281.0386439174</v>
+        <v>182668.3545783118</v>
       </c>
       <c r="D11" s="4" t="n">
-        <v>56693.05835035787</v>
+        <v>41995.84962910623</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>254162.644277216</v>
+        <v>100356.4893052636</v>
       </c>
       <c r="F11" s="5" t="n">
-        <v>476399.4330106188</v>
+        <v>264980.2198513601</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>0.8557117263347711</v>
+        <v>0.8254775277216394</v>
       </c>
       <c r="H11" s="7" t="n">
-        <v>0.0003525505122485738</v>
+        <v>0.01216017261644543</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>0.455–0.524</t>
+          <t>0.071–0.175</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>MI</t>
+          <t>ID</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Michigan</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>182668.3545783118</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>41995.84962910623</v>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>161365.7711350658</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>81369.14959500878</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>100356.4893052636</v>
+        <v>1882.237928848539</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>264980.2198513601</v>
+        <v>320849.304341283</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.8254775277216394</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.01216017261644543</v>
+        <v>0.3597256177062605</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.08777557523272957</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>0.071–0.175</t>
+          <t>0.011–0.136</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>MN</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Idaho</t>
+          <t>Minnesota</t>
         </is>
       </c>
       <c r="C13" s="5" t="n">
-        <v>161365.7711350658</v>
+        <v>159666.0767913745</v>
       </c>
       <c r="D13" s="5" t="n">
-        <v>81369.14959500878</v>
+        <v>70988.59979632952</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>1882.237928848539</v>
+        <v>20528.42119056868</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>320849.304341283</v>
+        <v>298803.7323921804</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3597256177062605</v>
+        <v>0.4195113867858169</v>
       </c>
       <c r="H13" s="8" t="n">
-        <v>0.08777557523272957</v>
+        <v>0.05926984185644371</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>0.011–0.136</t>
+          <t>0.131–0.227</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>MN</t>
+          <t>WI</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Minnesota</t>
-        </is>
-      </c>
-      <c r="C14" s="5" t="n">
-        <v>159666.0767913745</v>
-      </c>
-      <c r="D14" s="5" t="n">
-        <v>70988.59979632952</v>
+          <t>Wisconsin</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="n">
+        <v>141500.2570603061</v>
+      </c>
+      <c r="D14" s="4" t="n">
+        <v>59715.83302832763</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>20528.42119056868</v>
+        <v>24457.22432478397</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>298803.7323921804</v>
+        <v>258543.2897958283</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.4195113867858169</v>
-      </c>
-      <c r="H14" s="8" t="n">
-        <v>0.05926984185644371</v>
+        <v>0.4450969051680125</v>
+      </c>
+      <c r="H14" s="7" t="n">
+        <v>0.0496383190762822</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>0.131–0.227</t>
+          <t>0.039–0.174</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>WI</t>
+          <t>SD</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Wisconsin</t>
+          <t>South Dakota</t>
         </is>
       </c>
       <c r="C15" s="4" t="n">
-        <v>141500.2570603061</v>
+        <v>136467.3520923521</v>
       </c>
       <c r="D15" s="4" t="n">
-        <v>59715.83302832763</v>
+        <v>29286.7955435572</v>
       </c>
       <c r="E15" s="5" t="n">
-        <v>24457.22432478397</v>
+        <v>79065.23282697998</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>258543.2897958283</v>
+        <v>193869.4713577242</v>
       </c>
       <c r="G15" s="6" t="n">
-        <v>0.4450969051680125</v>
+        <v>0.756205436808266</v>
       </c>
       <c r="H15" s="7" t="n">
-        <v>0.0496383190762822</v>
+        <v>0.002315353524320524</v>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>0.039–0.174</t>
+          <t>0.002–0.042</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>TN</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>South Dakota</t>
+          <t>Tennessee</t>
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>136467.3520923521</v>
+        <v>110482.454529175</v>
       </c>
       <c r="D16" s="4" t="n">
-        <v>29286.7955435572</v>
+        <v>10452.76480246003</v>
       </c>
       <c r="E16" s="5" t="n">
-        <v>79065.23282697998</v>
+        <v>89995.03551635338</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>193869.4713577242</v>
+        <v>130969.8735419967</v>
       </c>
       <c r="G16" s="6" t="n">
-        <v>0.756205436808266</v>
+        <v>0.9410368855197646</v>
       </c>
       <c r="H16" s="7" t="n">
-        <v>0.002315353524320524</v>
+        <v>1.483122033163515e-05</v>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>0.002–0.042</t>
+          <t>0.178–0.553</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>TN</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Tennessee</t>
+          <t>California</t>
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>110482.454529175</v>
+        <v>99377.9952073465</v>
       </c>
       <c r="D17" s="4" t="n">
-        <v>10452.76480246003</v>
+        <v>22971.72044896776</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>89995.03551635338</v>
+        <v>54353.42312736968</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>130969.8735419967</v>
+        <v>144402.5672873233</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>0.9410368855197646</v>
+        <v>0.7277869751478535</v>
       </c>
       <c r="H17" s="7" t="n">
-        <v>1.483122033163515e-05</v>
+        <v>0.003454286025339076</v>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>0.178–0.553</t>
+          <t>2.118–3.474</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>CA</t>
+          <t>MO</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>California</t>
-        </is>
-      </c>
-      <c r="C18" s="4" t="n">
-        <v>99377.9952073465</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>22971.72044896776</v>
+          <t>Missouri</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>84060.81205110946</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>44494.22153910488</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>54353.42312736968</v>
+        <v>-3147.862165536106</v>
       </c>
       <c r="F18" s="5" t="n">
-        <v>144402.5672873233</v>
+        <v>171269.486267755</v>
       </c>
       <c r="G18" s="6" t="n">
-        <v>0.7277869751478535</v>
-      </c>
-      <c r="H18" s="7" t="n">
-        <v>0.003454286025339076</v>
+        <v>0.337702879272156</v>
+      </c>
+      <c r="H18" s="8" t="n">
+        <v>0.1007860717009649</v>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>2.118–3.474</t>
+          <t>0.167–0.344</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>MO</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Missouri</t>
+          <t>New Jersey</t>
         </is>
       </c>
       <c r="C19" s="5" t="n">
-        <v>84060.81205110946</v>
+        <v>78029.99428138971</v>
       </c>
       <c r="D19" s="5" t="n">
-        <v>44494.22153910488</v>
+        <v>50166.7975758298</v>
       </c>
       <c r="E19" s="5" t="n">
-        <v>-3147.862165536106</v>
+        <v>-20296.9289672367</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>171269.486267755</v>
+        <v>176356.9175300161</v>
       </c>
       <c r="G19" s="6" t="n">
-        <v>0.337702879272156</v>
+        <v>0.2568452819621015</v>
       </c>
       <c r="H19" s="8" t="n">
-        <v>0.1007860717009649</v>
+        <v>0.1637997890405266</v>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>0.167–0.344</t>
+          <t>0.903–0.991</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>IN</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-      <c r="C20" s="5" t="n">
-        <v>78029.99428138971</v>
-      </c>
-      <c r="D20" s="5" t="n">
-        <v>50166.7975758298</v>
+          <t>Indiana</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="n">
+        <v>76525.88046288324</v>
+      </c>
+      <c r="D20" s="4" t="n">
+        <v>12415.68835048377</v>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-20296.9289672367</v>
+        <v>52191.13129593506</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>176356.9175300161</v>
+        <v>100860.6296298314</v>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.2568452819621015</v>
-      </c>
-      <c r="H20" s="8" t="n">
-        <v>0.1637997890405266</v>
+        <v>0.8444116147156924</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>0.0004613363168796186</v>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>0.903–0.991</t>
+          <t>0.151–0.518</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Indiana</t>
+          <t>Montana</t>
         </is>
       </c>
       <c r="C21" s="4" t="n">
-        <v>76525.88046288324</v>
+        <v>74281.43909731616</v>
       </c>
       <c r="D21" s="4" t="n">
-        <v>12415.68835048377</v>
+        <v>15151.25860271623</v>
       </c>
       <c r="E21" s="5" t="n">
-        <v>52191.13129593506</v>
+        <v>44584.97223599236</v>
       </c>
       <c r="F21" s="5" t="n">
-        <v>100860.6296298314</v>
+        <v>103977.90595864</v>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.8444116147156924</v>
+        <v>0.77445587366291</v>
       </c>
       <c r="H21" s="7" t="n">
-        <v>0.0004613363168796186</v>
+        <v>0.001747820036840314</v>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>0.151–0.518</t>
+          <t>0.024–0.129</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Montana</t>
+          <t>North Carolina</t>
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>74281.43909731616</v>
+        <v>67177.10066031506</v>
       </c>
       <c r="D22" s="4" t="n">
-        <v>15151.25860271623</v>
+        <v>27311.55443529491</v>
       </c>
       <c r="E22" s="5" t="n">
-        <v>44584.97223599236</v>
+        <v>13646.45396713704</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>103977.90595864</v>
+        <v>120707.7473534931</v>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.77445587366291</v>
+        <v>0.4635982686637776</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.001747820036840314</v>
+        <v>0.04348707581747471</v>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>0.024–0.129</t>
+          <t>0.833–1.595</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>UT</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>North Carolina</t>
+          <t>Utah</t>
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>67177.10066031506</v>
+        <v>58916.33778936392</v>
       </c>
       <c r="D23" s="4" t="n">
-        <v>27311.55443529491</v>
+        <v>3801.261773790553</v>
       </c>
       <c r="E23" s="5" t="n">
-        <v>13646.45396713704</v>
+        <v>51465.86471273444</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>120707.7473534931</v>
+        <v>66366.81086599341</v>
       </c>
       <c r="G23" s="6" t="n">
-        <v>0.4635982686637776</v>
+        <v>0.9716855674823982</v>
       </c>
       <c r="H23" s="7" t="n">
-        <v>0.04348707581747471</v>
+        <v>1.124085594772211e-06</v>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>0.833–1.595</t>
+          <t>0.083–0.755</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>UT</t>
+          <t>AZ</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Utah</t>
+          <t>Arizona</t>
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>58916.33778936392</v>
+        <v>53618.32068587107</v>
       </c>
       <c r="D24" s="4" t="n">
-        <v>3801.261773790553</v>
+        <v>7904.523935945609</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>51465.86471273444</v>
+        <v>38125.45377141768</v>
       </c>
       <c r="F24" s="5" t="n">
-        <v>66366.81086599341</v>
+        <v>69111.18760032447</v>
       </c>
       <c r="G24" s="6" t="n">
-        <v>0.9716855674823982</v>
+        <v>0.8679554458491042</v>
       </c>
       <c r="H24" s="7" t="n">
-        <v>1.124085594772211e-06</v>
+        <v>0.000257095189419951</v>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>0.083–0.755</t>
+          <t>0.825–2.393</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>AZ</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Arizona</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n">
-        <v>53618.32068587107</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>7904.523935945609</v>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>48560.42695621782</v>
+      </c>
+      <c r="D25" s="5" t="n">
+        <v>37344.72285765477</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>38125.45377141768</v>
+        <v>-24635.22984478554</v>
       </c>
       <c r="F25" s="5" t="n">
-        <v>69111.18760032447</v>
+        <v>121756.0837572212</v>
       </c>
       <c r="G25" s="6" t="n">
-        <v>0.8679554458491042</v>
-      </c>
-      <c r="H25" s="7" t="n">
-        <v>0.000257095189419951</v>
+        <v>0.194555708934474</v>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>0.2346611920436925</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>0.825–2.393</t>
+          <t>0.335–0.408</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>48560.42695621782</v>
-      </c>
-      <c r="D26" s="5" t="n">
-        <v>37344.72285765477</v>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="n">
+        <v>46764.93241444086</v>
+      </c>
+      <c r="D26" s="4" t="n">
+        <v>7584.543968214312</v>
       </c>
       <c r="E26" s="5" t="n">
-        <v>-24635.22984478554</v>
+        <v>31899.22623674081</v>
       </c>
       <c r="F26" s="5" t="n">
-        <v>121756.0837572212</v>
+        <v>61630.63859214091</v>
       </c>
       <c r="G26" s="6" t="n">
-        <v>0.194555708934474</v>
-      </c>
-      <c r="H26" s="8" t="n">
-        <v>0.2346611920436925</v>
+        <v>0.8445043465500178</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>0.0004603555646732654</v>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>0.335–0.408</t>
+          <t>0.245–0.598</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>South Carolina</t>
+          <t>Washington</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46764.93241444086</v>
+        <v>42040.64390351795</v>
       </c>
       <c r="D27" s="4" t="n">
-        <v>7584.543968214312</v>
+        <v>9030.558157600231</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>31899.22623674081</v>
+        <v>24340.7499146215</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>61630.63859214091</v>
+        <v>59740.5378924144</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.8445043465500178</v>
+        <v>0.7558638529066335</v>
       </c>
       <c r="H27" s="7" t="n">
-        <v>0.0004603555646732654</v>
+        <v>0.002327117312896478</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>0.245–0.598</t>
+          <t>1.023–1.900</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>Alabama</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>42040.64390351795</v>
+        <v>38895.9063427481</v>
       </c>
       <c r="D28" s="4" t="n">
-        <v>9030.558157600231</v>
+        <v>5350.91416682027</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>24340.7499146215</v>
+        <v>28408.11457578037</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>59740.5378924144</v>
+        <v>49383.69810971583</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.7558638529066335</v>
+        <v>0.8830187772516441</v>
       </c>
       <c r="H28" s="7" t="n">
-        <v>0.002327117312896478</v>
+        <v>0.0001671615852347591</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>1.023–1.900</t>
+          <t>0.001–0.483</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Alabama</t>
+          <t>Nevada</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>38895.9063427481</v>
+        <v>29510.66630741444</v>
       </c>
       <c r="D29" s="4" t="n">
-        <v>5350.91416682027</v>
+        <v>6991.759259743158</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>28408.11457578037</v>
+        <v>15806.81815831785</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>49383.69810971583</v>
+        <v>43214.51445651102</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.8830187772516441</v>
+        <v>0.7179122131792786</v>
       </c>
       <c r="H29" s="7" t="n">
-        <v>0.0001671615852347591</v>
+        <v>0.003932808402513206</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>0.001–0.483</t>
+          <t>0.228–1.450</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>GA</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Nevada</t>
+          <t>Georgia</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>29510.66630741444</v>
+        <v>26838.86579410405</v>
       </c>
       <c r="D30" s="4" t="n">
-        <v>6991.759259743158</v>
+        <v>3367.364632354292</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>15806.81815831785</v>
+        <v>20238.83111468964</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>43214.51445651102</v>
+        <v>33438.90047351846</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.7179122131792786</v>
+        <v>0.9007451067710492</v>
       </c>
       <c r="H30" s="7" t="n">
-        <v>0.003932808402513206</v>
+        <v>9.334003260746483e-05</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>0.228–1.450</t>
+          <t>0.913–2.559</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>GA</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Georgia</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>26838.86579410405</v>
+        <v>18124.93655291465</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>3367.364632354292</v>
+        <v>2824.27863286161</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>20238.83111468964</v>
+        <v>12589.35043250589</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>33438.90047351846</v>
+        <v>23660.5226733234</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.9007451067710492</v>
+        <v>0.8547262426858913</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>9.334003260746483e-05</v>
+        <v>0.0003612080306820614</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>0.913–2.559</t>
+          <t>2.502–8.943</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Texas</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C32" s="4" t="n">
-        <v>18124.93655291465</v>
+        <v>15831.10289458326</v>
       </c>
       <c r="D32" s="4" t="n">
-        <v>2824.27863286161</v>
+        <v>5557.254449287901</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>12589.35043250589</v>
+        <v>4938.884173978979</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>23660.5226733234</v>
+        <v>26723.32161518755</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.8547262426858913</v>
+        <v>0.5368914786139682</v>
       </c>
       <c r="H32" s="7" t="n">
-        <v>0.0003612080306820614</v>
+        <v>0.02473346892323111</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>2.502–8.943</t>
+          <t>0.298–0.930</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>15831.10289458326</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>5557.254449287901</v>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>15485.59029929344</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>8860.136130807245</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>4938.884173978979</v>
+        <v>-1880.276517088758</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>26723.32161518755</v>
+        <v>32851.45711567564</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.5368914786139682</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>0.02473346892323111</v>
+        <v>0.3038111770617528</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0.1239935225964218</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>0.298–0.930</t>
+          <t>0.174–0.286</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>15485.59029929344</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>8860.136130807245</v>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>15431.42429686791</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>3577.258690109372</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-1880.276517088758</v>
+        <v>8419.997264253536</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>32851.45711567564</v>
+        <v>22442.85132948228</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.3038111770617528</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>0.1239935225964218</v>
+        <v>0.7266532430719608</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>0.00350691319047221</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>0.174–0.286</t>
+          <t>0.007–0.562</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="n">
-        <v>15431.42429686791</v>
-      </c>
-      <c r="D35" s="4" t="n">
-        <v>3577.258690109372</v>
+          <t>Maryland</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="n">
+        <v>13968.45401143807</v>
+      </c>
+      <c r="D35" s="5" t="n">
+        <v>18864.27279561335</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>8419.997264253536</v>
+        <v>-23005.5206679641</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>22442.85132948228</v>
+        <v>50942.42869084024</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.7266532430719608</v>
-      </c>
-      <c r="H35" s="7" t="n">
-        <v>0.00350691319047221</v>
+        <v>0.07263860903256718</v>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>0.4831059422988369</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>0.007–0.562</t>
+          <t>0.078–0.171</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Maryland</t>
-        </is>
-      </c>
-      <c r="C36" s="5" t="n">
-        <v>13968.45401143807</v>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>18864.27279561335</v>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="n">
+        <v>13840.35892950911</v>
+      </c>
+      <c r="D36" s="4" t="n">
+        <v>2371.386707988194</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-23005.5206679641</v>
+        <v>9192.440981852251</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>50942.42869084024</v>
+        <v>18488.27687716597</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.07263860903256718</v>
-      </c>
-      <c r="H36" s="8" t="n">
-        <v>0.4831059422988369</v>
+        <v>0.8295325292597641</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>0.0006393766281142857</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>0.078–0.171</t>
+          <t>0.351–2.435</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="n">
-        <v>13840.35892950911</v>
-      </c>
-      <c r="D37" s="4" t="n">
-        <v>2371.386707988194</v>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="n">
+        <v>11216.96260116209</v>
+      </c>
+      <c r="D37" s="5" t="n">
+        <v>5670.234271715624</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>9192.440981852251</v>
+        <v>103.3034285994618</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>18488.27687716597</v>
+        <v>22330.62177372471</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.8295325292597641</v>
-      </c>
-      <c r="H37" s="7" t="n">
-        <v>0.0006393766281142857</v>
+        <v>0.3585836717608015</v>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>0.08841367505002616</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>0.351–2.435</t>
+          <t>0.450–1.512</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>IL</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C38" s="5" t="n">
-        <v>11216.96260116209</v>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>5670.234271715624</v>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="n">
+        <v>10608.71915386618</v>
+      </c>
+      <c r="D38" s="4" t="n">
+        <v>2945.394875406134</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>103.3034285994618</v>
+        <v>4835.745198070159</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>22330.62177372471</v>
+        <v>16381.6931096622</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.3585836717608015</v>
-      </c>
-      <c r="H38" s="8" t="n">
-        <v>0.08841367505002616</v>
+        <v>0.6495260399062091</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>0.008718896133129976</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>0.450–1.512</t>
+          <t>1.250–2.805</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>IL</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Illinois</t>
+          <t>Nebraska</t>
         </is>
       </c>
       <c r="C39" s="4" t="n">
-        <v>10608.71915386618</v>
+        <v>8725.673436479692</v>
       </c>
       <c r="D39" s="4" t="n">
-        <v>2945.394875406134</v>
+        <v>1044.252295555334</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>4835.745198070159</v>
+        <v>6678.938937191238</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>16381.6931096622</v>
+        <v>10772.40793576815</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.6495260399062091</v>
+        <v>0.9088792672384642</v>
       </c>
       <c r="H39" s="7" t="n">
-        <v>0.008718896133129976</v>
+        <v>6.896091173039629e-05</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>1.250–2.805</t>
+          <t>0.069–1.256</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C40" s="4" t="n">
-        <v>8725.673436479692</v>
+        <v>6296.286147200562</v>
       </c>
       <c r="D40" s="4" t="n">
-        <v>1044.252295555334</v>
+        <v>1718.358191584645</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>6678.938937191238</v>
+        <v>2928.304091694658</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>10772.40793576815</v>
+        <v>9664.268202706466</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.9088792672384642</v>
+        <v>0.6572968627174608</v>
       </c>
       <c r="H40" s="7" t="n">
-        <v>6.896091173039629e-05</v>
+        <v>0.008026336208281932</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>0.069–1.256</t>
+          <t>0.822–2.238</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="n">
-        <v>6296.286147200562</v>
-      </c>
-      <c r="D41" s="4" t="n">
-        <v>1718.358191584645</v>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="n">
+        <v>6132.376016596852</v>
+      </c>
+      <c r="D41" s="5" t="n">
+        <v>15946.16340322553</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>2928.304091694658</v>
+        <v>-25122.10425372519</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>9664.268202706466</v>
+        <v>37386.8562869189</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.6572968627174608</v>
-      </c>
-      <c r="H41" s="7" t="n">
-        <v>0.008026336208281932</v>
+        <v>0.0206903168509888</v>
+      </c>
+      <c r="H41" s="8" t="n">
+        <v>0.7119744254744499</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>0.822–2.238</t>
+          <t>0.453–0.917</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>New York</t>
-        </is>
-      </c>
-      <c r="C42" s="5" t="n">
-        <v>6132.376016596852</v>
-      </c>
-      <c r="D42" s="5" t="n">
-        <v>15946.16340322553</v>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="n">
+        <v>5965.21535186114</v>
+      </c>
+      <c r="D42" s="4" t="n">
+        <v>1398.254107341866</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-25122.10425372519</v>
+        <v>3224.637301471084</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>37386.8562869189</v>
+        <v>8705.793402251196</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.0206903168509888</v>
-      </c>
-      <c r="H42" s="8" t="n">
-        <v>0.7119744254744499</v>
+        <v>0.7222262218026829</v>
+      </c>
+      <c r="H42" s="7" t="n">
+        <v>0.003718103768988485</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>0.453–0.917</t>
+          <t>0.687–4.588</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Virginia</t>
         </is>
       </c>
       <c r="C43" s="4" t="n">
-        <v>5965.21535186114</v>
+        <v>4614.056073272084</v>
       </c>
       <c r="D43" s="4" t="n">
-        <v>1398.254107341866</v>
+        <v>472.3035228783646</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>3224.637301471084</v>
+        <v>3688.34116843049</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>8705.793402251196</v>
+        <v>5539.770978113678</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.7222262218026829</v>
+        <v>0.9316662818687531</v>
       </c>
       <c r="H43" s="7" t="n">
-        <v>0.003718103768988485</v>
+        <v>2.494825574552957e-05</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>0.687–4.588</t>
+          <t>2.006–8.240</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="n">
-        <v>4614.056073272084</v>
-      </c>
-      <c r="D44" s="4" t="n">
-        <v>472.3035228783646</v>
+          <t>North Dakota</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>335.9623410461367</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>1240.261153541205</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>3688.34116843049</v>
+        <v>-2094.949519894625</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>5539.770978113678</v>
+        <v>2766.874201986898</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.9316662818687531</v>
-      </c>
-      <c r="H44" s="7" t="n">
-        <v>2.494825574552957e-05</v>
+        <v>0.01037356807843008</v>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>0.7942967292409999</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>2.006–8.240</t>
+          <t>0.240–1.469</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="C45" s="5" t="n">
-        <v>335.9623410461367</v>
+        <v>-4680.768843378283</v>
       </c>
       <c r="D45" s="5" t="n">
-        <v>1240.261153541205</v>
+        <v>10561.44832620658</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-2094.949519894625</v>
+        <v>-25381.20756274318</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>2766.874201986898</v>
+        <v>16019.66987598662</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.01037356807843008</v>
+        <v>0.02729423224792807</v>
       </c>
       <c r="H45" s="8" t="n">
-        <v>0.7942967292409999</v>
+        <v>0.6709990996682395</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>0.240–1.469</t>
+          <t>0.035–0.069</t>
         </is>
       </c>
     </row>
@@ -2261,12 +2261,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C50" s="5" t="n"/>
@@ -2277,19 +2277,19 @@
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>0.000–0.000</t>
+          <t>0.002–0.002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="C51" s="5" t="n"/>
@@ -2299,29 +2299,6 @@
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>0.002–0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>0.015–0.015</t>
         </is>
@@ -2343,7 +2320,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3260,665 +3237,665 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>WA</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Washington</t>
+          <t>District of Columbia</t>
         </is>
       </c>
       <c r="C27" s="5" t="n">
-        <v>3018.00502820463</v>
+        <v>3458.345243561805</v>
       </c>
       <c r="D27" s="5" t="n">
-        <v>1548.954013140705</v>
+        <v>2377.852905389024</v>
       </c>
       <c r="E27" s="5" t="n">
-        <v>-17.94483755115243</v>
+        <v>-1202.246451000682</v>
       </c>
       <c r="F27" s="5" t="n">
-        <v>6053.954893960412</v>
+        <v>8118.936938124291</v>
       </c>
       <c r="G27" s="6" t="n">
-        <v>0.3516309558631755</v>
+        <v>0.2320582286184664</v>
       </c>
       <c r="H27" s="8" t="n">
-        <v>0.09238299447244565</v>
+        <v>0.1891596687614609</v>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>1.023–1.900</t>
+          <t>0.035–0.069</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>NV</t>
+          <t>WA</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Nevada</t>
-        </is>
-      </c>
-      <c r="C28" s="4" t="n">
-        <v>2154.624330844884</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>910.6651342520753</v>
+          <t>Washington</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3018.00502820463</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>1548.954013140705</v>
       </c>
       <c r="E28" s="5" t="n">
-        <v>369.7206677108168</v>
+        <v>-17.94483755115243</v>
       </c>
       <c r="F28" s="5" t="n">
-        <v>3939.527993978952</v>
+        <v>6053.954893960412</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>0.4443521573521072</v>
-      </c>
-      <c r="H28" s="7" t="n">
-        <v>0.0498996767651404</v>
+        <v>0.3516309558631755</v>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>0.09238299447244565</v>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>0.228–1.450</t>
+          <t>1.023–1.900</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>NM</t>
+          <t>NV</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="C29" s="5" t="n">
-        <v>1649.22997013761</v>
-      </c>
-      <c r="D29" s="5" t="n">
-        <v>1166.065390482135</v>
+          <t>Nevada</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="n">
+        <v>2154.624330844884</v>
+      </c>
+      <c r="D29" s="4" t="n">
+        <v>910.6651342520753</v>
       </c>
       <c r="E29" s="5" t="n">
-        <v>-636.2581952073749</v>
+        <v>369.7206677108168</v>
       </c>
       <c r="F29" s="5" t="n">
-        <v>3934.718135482595</v>
+        <v>3939.527993978952</v>
       </c>
       <c r="G29" s="6" t="n">
-        <v>0.222256700964437</v>
-      </c>
-      <c r="H29" s="8" t="n">
-        <v>0.200160331619509</v>
+        <v>0.4443521573521072</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>0.0498996767651404</v>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>0.007–0.562</t>
+          <t>0.228–1.450</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>OH</t>
+          <t>NM</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="n">
-        <v>1368.954076930735</v>
-      </c>
-      <c r="D30" s="4" t="n">
-        <v>512.7926555430249</v>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="n">
+        <v>1649.22997013761</v>
+      </c>
+      <c r="D30" s="5" t="n">
+        <v>1166.065390482135</v>
       </c>
       <c r="E30" s="5" t="n">
-        <v>363.8804720664062</v>
+        <v>-636.2581952073749</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>2374.027681795064</v>
+        <v>3934.718135482595</v>
       </c>
       <c r="G30" s="6" t="n">
-        <v>0.5044876904806943</v>
-      </c>
-      <c r="H30" s="7" t="n">
-        <v>0.03201799771992795</v>
+        <v>0.222256700964437</v>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>0.200160331619509</v>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>0.351–2.435</t>
+          <t>0.007–0.562</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>NE</t>
+          <t>OH</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Nebraska</t>
+          <t>Ohio</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1149.17579647689</v>
+        <v>1368.954076930735</v>
       </c>
       <c r="D31" s="4" t="n">
-        <v>216.2312986640796</v>
+        <v>512.7926555430249</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>725.3624510952936</v>
+        <v>363.8804720664062</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>1572.989141858486</v>
+        <v>2374.027681795064</v>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.8013881602738087</v>
+        <v>0.5044876904806943</v>
       </c>
       <c r="H31" s="7" t="n">
-        <v>0.00110576035134234</v>
+        <v>0.03201799771992795</v>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>0.069–1.256</t>
+          <t>0.351–2.435</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>PA</t>
+          <t>NE</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Pennsylvania</t>
-        </is>
-      </c>
-      <c r="C32" s="5" t="n">
-        <v>968.4222386702635</v>
-      </c>
-      <c r="D32" s="5" t="n">
-        <v>798.4709954249789</v>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n">
+        <v>1149.17579647689</v>
+      </c>
+      <c r="D32" s="4" t="n">
+        <v>216.2312986640796</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-596.5809123626951</v>
+        <v>725.3624510952936</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>2533.425389703222</v>
+        <v>1572.989141858486</v>
       </c>
       <c r="G32" s="6" t="n">
-        <v>0.173650800174989</v>
-      </c>
-      <c r="H32" s="8" t="n">
-        <v>0.2645258195735226</v>
+        <v>0.8013881602738087</v>
+      </c>
+      <c r="H32" s="7" t="n">
+        <v>0.00110576035134234</v>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>0.450–1.512</t>
+          <t>0.069–1.256</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>VA</t>
+          <t>PA</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Virginia</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>910.2637073328453</v>
-      </c>
-      <c r="D33" s="4" t="n">
-        <v>113.6882021913307</v>
+          <t>Pennsylvania</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>968.4222386702635</v>
+      </c>
+      <c r="D33" s="5" t="n">
+        <v>798.4709954249789</v>
       </c>
       <c r="E33" s="5" t="n">
-        <v>687.4348310378371</v>
+        <v>-596.5809123626951</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1133.092583627854</v>
+        <v>2533.425389703222</v>
       </c>
       <c r="G33" s="6" t="n">
-        <v>0.9015564416520166</v>
-      </c>
-      <c r="H33" s="7" t="n">
-        <v>9.066555097079382e-05</v>
+        <v>0.173650800174989</v>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>0.2645258195735226</v>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>2.006–8.240</t>
+          <t>0.450–1.512</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>TX</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Texas</t>
-        </is>
-      </c>
-      <c r="C34" s="5" t="n">
-        <v>743.2619761354642</v>
-      </c>
-      <c r="D34" s="5" t="n">
-        <v>1174.881412208036</v>
+          <t>Virginia</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="n">
+        <v>910.2637073328453</v>
+      </c>
+      <c r="D34" s="4" t="n">
+        <v>113.6882021913307</v>
       </c>
       <c r="E34" s="5" t="n">
-        <v>-1559.505591792287</v>
+        <v>687.4348310378371</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3046.029544063215</v>
+        <v>1133.092583627854</v>
       </c>
       <c r="G34" s="6" t="n">
-        <v>0.05408181996121192</v>
-      </c>
-      <c r="H34" s="8" t="n">
-        <v>0.5470779911801144</v>
+        <v>0.9015564416520166</v>
+      </c>
+      <c r="H34" s="7" t="n">
+        <v>9.066555097079382e-05</v>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>2.502–8.943</t>
+          <t>2.006–8.240</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>OR</t>
+          <t>TX</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Oregon</t>
+          <t>Texas</t>
         </is>
       </c>
       <c r="C35" s="5" t="n">
-        <v>364.6951435501712</v>
+        <v>743.2619761354642</v>
       </c>
       <c r="D35" s="5" t="n">
-        <v>210.8450639111911</v>
+        <v>1174.881412208036</v>
       </c>
       <c r="E35" s="5" t="n">
-        <v>-48.56118171576333</v>
+        <v>-1559.505591792287</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>777.9514688161057</v>
+        <v>3046.029544063215</v>
       </c>
       <c r="G35" s="6" t="n">
-        <v>0.2994257829524181</v>
+        <v>0.05408181996121192</v>
       </c>
       <c r="H35" s="8" t="n">
-        <v>0.1273088107620285</v>
+        <v>0.5470779911801144</v>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>0.687–4.588</t>
+          <t>2.502–8.943</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>KY</t>
+          <t>OR</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Kentucky</t>
+          <t>Oregon</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
-        <v>237.7754778089678</v>
+        <v>364.6951435501712</v>
       </c>
       <c r="D36" s="5" t="n">
-        <v>876.2682464994331</v>
+        <v>210.8450639111911</v>
       </c>
       <c r="E36" s="5" t="n">
-        <v>-1479.710285329921</v>
+        <v>-48.56118171576333</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>1955.261240947857</v>
+        <v>777.9514688161057</v>
       </c>
       <c r="G36" s="6" t="n">
-        <v>0.01040920553654912</v>
+        <v>0.2994257829524181</v>
       </c>
       <c r="H36" s="8" t="n">
-        <v>0.7939498095893049</v>
+        <v>0.1273088107620285</v>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>0.298–0.930</t>
+          <t>0.687–4.588</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>IA</t>
+          <t>KY</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Iowa</t>
+          <t>Kentucky</t>
         </is>
       </c>
       <c r="C37" s="5" t="n">
-        <v>-91.95692003202824</v>
+        <v>237.7754778089678</v>
       </c>
       <c r="D37" s="5" t="n">
-        <v>464.3634785318953</v>
+        <v>876.2682464994331</v>
       </c>
       <c r="E37" s="5" t="n">
-        <v>-1002.109337954543</v>
+        <v>-1479.710285329921</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>818.1954978904864</v>
+        <v>1955.261240947857</v>
       </c>
       <c r="G37" s="6" t="n">
-        <v>0.005570940101006342</v>
+        <v>0.01040920553654912</v>
       </c>
       <c r="H37" s="8" t="n">
-        <v>0.8486513556265166</v>
+        <v>0.7939498095893049</v>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>0.822–2.238</t>
+          <t>0.298–0.930</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>ND</t>
+          <t>IA</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>North Dakota</t>
+          <t>Iowa</t>
         </is>
       </c>
       <c r="C38" s="5" t="n">
-        <v>-570.7949376903085</v>
+        <v>-91.95692003202824</v>
       </c>
       <c r="D38" s="5" t="n">
-        <v>272.5946861708682</v>
+        <v>464.3634785318953</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>-1105.08052258521</v>
+        <v>-1002.109337954543</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>-36.50935279540681</v>
+        <v>818.1954978904864</v>
       </c>
       <c r="G38" s="6" t="n">
-        <v>0.3851318367368298</v>
+        <v>0.005570940101006342</v>
       </c>
       <c r="H38" s="8" t="n">
-        <v>0.07453595526879217</v>
+        <v>0.8486513556265166</v>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>0.240–1.469</t>
+          <t>0.822–2.238</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>WY</t>
+          <t>ND</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Wyoming</t>
+          <t>North Dakota</t>
         </is>
       </c>
       <c r="C39" s="5" t="n">
-        <v>-1002.864934968989</v>
+        <v>-570.7949376903085</v>
       </c>
       <c r="D39" s="5" t="n">
-        <v>715.4644761631931</v>
+        <v>272.5946861708682</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>-2405.175308248848</v>
+        <v>-1105.08052258521</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>399.4454383108692</v>
+        <v>-36.50935279540681</v>
       </c>
       <c r="G39" s="6" t="n">
-        <v>0.2191645170954686</v>
+        <v>0.3851318367368298</v>
       </c>
       <c r="H39" s="8" t="n">
-        <v>0.2037545707527143</v>
+        <v>0.07453595526879217</v>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>0.174–0.286</t>
+          <t>0.240–1.469</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>NY</t>
+          <t>WY</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>New York</t>
+          <t>Wyoming</t>
         </is>
       </c>
       <c r="C40" s="5" t="n">
-        <v>-5206.043762916461</v>
+        <v>-1002.864934968989</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>2291.877094537126</v>
+        <v>715.4644761631931</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>-9698.122868209226</v>
+        <v>-2405.175308248848</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>-713.9646576236946</v>
+        <v>399.4454383108692</v>
       </c>
       <c r="G40" s="6" t="n">
-        <v>0.4243327003253518</v>
+        <v>0.2191645170954686</v>
       </c>
       <c r="H40" s="8" t="n">
-        <v>0.05734884701200656</v>
+        <v>0.2037545707527143</v>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>0.453–0.917</t>
+          <t>0.174–0.286</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>MD</t>
+          <t>NY</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Maryland</t>
+          <t>New York</t>
         </is>
       </c>
       <c r="C41" s="5" t="n">
-        <v>-12011.17397059195</v>
+        <v>-5206.043762916461</v>
       </c>
       <c r="D41" s="5" t="n">
-        <v>7679.150724863124</v>
+        <v>2291.877094537126</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-27062.30939132367</v>
+        <v>-9698.122868209226</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>3039.961450139777</v>
+        <v>-713.9646576236946</v>
       </c>
       <c r="G41" s="6" t="n">
-        <v>0.258984504633035</v>
+        <v>0.4243327003253518</v>
       </c>
       <c r="H41" s="8" t="n">
-        <v>0.1617643656746395</v>
+        <v>0.05734884701200656</v>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>0.078–0.171</t>
+          <t>0.453–0.917</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>CT</t>
+          <t>MD</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Connecticut</t>
+          <t>Maryland</t>
         </is>
       </c>
       <c r="C42" s="5" t="n">
-        <v>-15584.68577900047</v>
+        <v>-12011.17397059195</v>
       </c>
       <c r="D42" s="5" t="n">
-        <v>36217.91104090708</v>
+        <v>7679.150724863124</v>
       </c>
       <c r="E42" s="5" t="n">
-        <v>-86571.79141917835</v>
+        <v>-27062.30939132367</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>55402.4198611774</v>
+        <v>3039.961450139777</v>
       </c>
       <c r="G42" s="6" t="n">
-        <v>0.02576990437139158</v>
+        <v>0.258984504633035</v>
       </c>
       <c r="H42" s="8" t="n">
-        <v>0.6799125554771166</v>
+        <v>0.1617643656746395</v>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>0.043–0.049</t>
+          <t>0.078–0.171</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>MA</t>
+          <t>CT</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="C43" s="9" t="n">
-        <v>-32923.52037493999</v>
-      </c>
-      <c r="D43" s="9" t="n">
-        <v>11552.10469683431</v>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="n">
+        <v>-15584.68577900047</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>36217.91104090708</v>
       </c>
       <c r="E43" s="5" t="n">
-        <v>-55565.64558073522</v>
+        <v>-86571.79141917835</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>-10281.39516914475</v>
+        <v>55402.4198611774</v>
       </c>
       <c r="G43" s="6" t="n">
-        <v>0.5371139045915381</v>
-      </c>
-      <c r="H43" s="10" t="n">
-        <v>0.02468837234659287</v>
+        <v>0.02576990437139158</v>
+      </c>
+      <c r="H43" s="8" t="n">
+        <v>0.6799125554771166</v>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>0.315–0.372</t>
+          <t>0.043–0.049</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>NH</t>
+          <t>MA</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>New Hampshire</t>
+          <t>Massachusetts</t>
         </is>
       </c>
       <c r="C44" s="9" t="n">
-        <v>-46182.12431588792</v>
+        <v>-32923.52037493999</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>14823.44440021923</v>
+        <v>11552.10469683431</v>
       </c>
       <c r="E44" s="5" t="n">
-        <v>-75236.07534031761</v>
+        <v>-55565.64558073522</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>-17128.17329145822</v>
+        <v>-10281.39516914475</v>
       </c>
       <c r="G44" s="6" t="n">
-        <v>0.5809940611088542</v>
+        <v>0.5371139045915381</v>
       </c>
       <c r="H44" s="10" t="n">
-        <v>0.0169506516202204</v>
+        <v>0.02468837234659287</v>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>0.001–0.005</t>
+          <t>0.315–0.372</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>NH</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="C45" s="5" t="n">
-        <v>-198854.1666666665</v>
-      </c>
-      <c r="D45" s="5" t="n">
-        <v>154587.7241045497</v>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C45" s="9" t="n">
+        <v>-46182.12431588792</v>
+      </c>
+      <c r="D45" s="9" t="n">
+        <v>14823.44440021923</v>
       </c>
       <c r="E45" s="5" t="n">
-        <v>-501846.105911584</v>
+        <v>-75236.07534031761</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>104137.7725782509</v>
+        <v>-17128.17329145822</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>0.1911909552770819</v>
-      </c>
-      <c r="H45" s="8" t="n">
-        <v>0.2392287085963752</v>
+        <v>0.5809940611088542</v>
+      </c>
+      <c r="H45" s="10" t="n">
+        <v>0.0169506516202204</v>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>0.016–0.017</t>
+          <t>0.001–0.005</t>
         </is>
       </c>
     </row>
@@ -4065,12 +4042,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C50" s="5" t="n"/>
@@ -4081,19 +4058,19 @@
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>0.000–0.000</t>
+          <t>0.002–0.002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="C51" s="5" t="n"/>
@@ -4103,29 +4080,6 @@
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>0.002–0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>0.015–0.015</t>
         </is>
@@ -4147,7 +4101,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I52"/>
+  <dimension ref="A1:I51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -4539,105 +4493,105 @@
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>HI</t>
+          <t>NJ</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="n">
-        <v>268229.1666666665</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>65972.14553305903</v>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>84707.15546568386</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>46916.76388619368</v>
       </c>
       <c r="E12" s="5" t="n">
-        <v>138923.7614218708</v>
+        <v>-7249.70175125575</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>397534.5719114622</v>
+        <v>176664.0126826235</v>
       </c>
       <c r="G12" s="6" t="n">
-        <v>0.7025160656928339</v>
-      </c>
-      <c r="H12" s="7" t="n">
-        <v>0.004774514463511854</v>
+        <v>0.3177220691791325</v>
+      </c>
+      <c r="H12" s="8" t="n">
+        <v>0.113967022319853</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>0.016–0.017</t>
+          <t>0.903–0.991</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
-          <t>NJ</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="n">
-        <v>84707.15546568386</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>46916.76388619368</v>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="n">
+        <v>50158.17641790877</v>
+      </c>
+      <c r="D13" s="4" t="n">
+        <v>11079.0121769848</v>
       </c>
       <c r="E13" s="5" t="n">
-        <v>-7249.70175125575</v>
+        <v>28443.31255101856</v>
       </c>
       <c r="F13" s="5" t="n">
-        <v>176664.0126826235</v>
+        <v>71873.04028479898</v>
       </c>
       <c r="G13" s="6" t="n">
-        <v>0.3177220691791325</v>
-      </c>
-      <c r="H13" s="8" t="n">
-        <v>0.113967022319853</v>
+        <v>0.745422883510992</v>
+      </c>
+      <c r="H13" s="7" t="n">
+        <v>0.0027083800241307</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>0.903–0.991</t>
+          <t>0.335–0.408</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>DC</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="n">
-        <v>50158.17641790877</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>11079.0121769848</v>
+          <t>District of Columbia</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>32263.99790262781</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>22719.2015290446</v>
       </c>
       <c r="E14" s="5" t="n">
-        <v>28443.31255101856</v>
+        <v>-12265.63709429962</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>71873.04028479898</v>
+        <v>76793.63289955523</v>
       </c>
       <c r="G14" s="6" t="n">
-        <v>0.745422883510992</v>
-      </c>
-      <c r="H14" s="7" t="n">
-        <v>0.0027083800241307</v>
+        <v>0.2236663316203038</v>
+      </c>
+      <c r="H14" s="8" t="n">
+        <v>0.1985418860715555</v>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>0.335–0.408</t>
+          <t>0.035–0.069</t>
         </is>
       </c>
     </row>
@@ -5869,12 +5823,12 @@
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>AK</t>
+          <t>AR</t>
         </is>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Alaska</t>
+          <t>Arkansas</t>
         </is>
       </c>
       <c r="C50" s="5" t="n"/>
@@ -5885,19 +5839,19 @@
       <c r="H50" s="8" t="n"/>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>0.000–0.000</t>
+          <t>0.002–0.002</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="inlineStr">
         <is>
-          <t>AR</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Arkansas</t>
+          <t>Delaware</t>
         </is>
       </c>
       <c r="C51" s="5" t="n"/>
@@ -5907,29 +5861,6 @@
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="3" t="inlineStr">
-        <is>
-          <t>0.002–0.002</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="3" t="inlineStr">
-        <is>
-          <t>DE</t>
-        </is>
-      </c>
-      <c r="B52" s="3" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-      <c r="C52" s="5" t="n"/>
-      <c r="D52" s="5" t="n"/>
-      <c r="E52" s="5" t="n"/>
-      <c r="F52" s="5" t="n"/>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="8" t="n"/>
-      <c r="I52" s="3" t="inlineStr">
         <is>
           <t>0.015–0.015</t>
         </is>
@@ -6756,18 +6687,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="10" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6796,7 +6729,8 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>SE
-(clustered)</t>
+(clustered,
+linearmodels)</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -6823,7 +6757,20 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>N obs / States</t>
+          <t>N obs / Units</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>SE
+(CGM-corrected,
+SI convention)</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>p-value
+t(G−1)</t>
         </is>
       </c>
     </row>
@@ -6839,27 +6786,33 @@
         </is>
       </c>
       <c r="C3" s="20" t="n">
-        <v>9146.011717841404</v>
+        <v>9159.744962096383</v>
       </c>
       <c r="D3" s="20" t="n">
-        <v>4423.815934814912</v>
+        <v>4419.298812539646</v>
       </c>
       <c r="E3" s="20" t="n">
-        <v>475.3324856041763</v>
+        <v>497.919289518677</v>
       </c>
       <c r="F3" s="20" t="n">
-        <v>17816.69095007863</v>
+        <v>17821.57063467409</v>
       </c>
       <c r="G3" s="7" t="n">
-        <v>0.03936841545296876</v>
+        <v>0.03887676538280105</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>0.2209633501516062</v>
+        <v>0.2211478204974701</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>439 / 50.0</t>
-        </is>
+          <t>438 / 49.0</t>
+        </is>
+      </c>
+      <c r="J3" s="21" t="n">
+        <v>4459.995824269214</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0.0454682313954794</v>
       </c>
     </row>
     <row r="4">
@@ -6874,27 +6827,33 @@
         </is>
       </c>
       <c r="C4" s="20" t="n">
-        <v>709.2047083319623</v>
+        <v>704.0797515808242</v>
       </c>
       <c r="D4" s="20" t="n">
-        <v>205.5625443344711</v>
+        <v>204.3931509230534</v>
       </c>
       <c r="E4" s="20" t="n">
-        <v>306.3021214363988</v>
+        <v>303.4691757716396</v>
       </c>
       <c r="F4" s="20" t="n">
-        <v>1112.107295227526</v>
+        <v>1104.690327390009</v>
       </c>
       <c r="G4" s="7" t="n">
-        <v>0.0006233312842884864</v>
+        <v>0.0006353803248111412</v>
       </c>
       <c r="H4" s="6" t="n">
-        <v>0.09365752802366301</v>
+        <v>0.09335166488941227</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>439 / 50.0</t>
-        </is>
+          <t>438 / 49.0</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="n">
+        <v>206.275393064489</v>
+      </c>
+      <c r="K4" s="8" t="n">
+        <v>0.001312792630527663</v>
       </c>
     </row>
     <row r="5">
@@ -6909,27 +6868,33 @@
         </is>
       </c>
       <c r="C5" s="21" t="n">
-        <v>8683.479737947244</v>
+        <v>8697.135687351078</v>
       </c>
       <c r="D5" s="21" t="n">
-        <v>5363.135340952423</v>
+        <v>5356.176949503176</v>
       </c>
       <c r="E5" s="21" t="n">
-        <v>-1828.265530319504</v>
+        <v>-1800.971133675146</v>
       </c>
       <c r="F5" s="21" t="n">
-        <v>19195.22500621399</v>
+        <v>19195.2425083773</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>0.1062542627624605</v>
+        <v>0.1052566356968134</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>0.4060281710564897</v>
+        <v>0.4060446314846675</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>439 / 50.0</t>
-        </is>
+          <t>438 / 49.0</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="n">
+        <v>5405.501606057527</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>0.1141874002103802</v>
       </c>
     </row>
     <row r="7">
@@ -6959,7 +6924,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>State (entity) + Year (time)</t>
+          <t>Unit (entity) + Year (time)</t>
         </is>
       </c>
     </row>
@@ -6971,25 +6936,45 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Clustered by state</t>
+          <t>Clustered by unit; linearmodels sandwich and the</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="23" t="inlineStr">
+      <c r="A11" s="23" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Cameron-Gelbach-Miller finite-sample correction both reported</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="inlineStr">
+        <is>
+          <t>Universe</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>the 48 contiguous states plus the District of Columbia (49 units)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="inlineStr">
         <is>
           <t>Period</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>2016–2024 (9 years)</t>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>2016–2024 (9 years); Michigan absent 2022–2024</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
